--- a/api/templates/module_status_report/uk.xlsx
+++ b/api/templates/module_status_report/uk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\opewix\dev\sysone\sources\aspect\api\templates\module_status_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F533FEB9-6EA7-4270-ADAA-7F80F6046DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F3FFAD-0DAE-4299-9B03-85E387222E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Звіт про статус модуля</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>&lt;disabledModules&gt;</t>
+  </si>
+  <si>
+    <t>* Модулі позначені як "Не використовуються" на момент формування звіту &lt;ReportDate&gt;</t>
   </si>
 </sst>
 </file>
@@ -122,7 +125,8 @@
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="12"/>
@@ -606,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="1"/>
@@ -712,6 +716,11 @@
         <v>23</v>
       </c>
     </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A8:I9" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/api/templates/module_status_report/uk.xlsx
+++ b/api/templates/module_status_report/uk.xlsx
@@ -1,34 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\opewix\dev\sysone\sources\aspect\api\templates\module_status_report\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F3FFAD-0DAE-4299-9B03-85E387222E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990"/>
   </bookViews>
   <sheets>
-    <sheet name="ModuleStatus" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="ModuleStatus" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ModuleStatus!$A$8:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase">ModuleStatus!$A$8:$I$9</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Звіт про статус модуля</t>
   </si>
@@ -54,6 +43,9 @@
     <t>Ім'я пристрою</t>
   </si>
   <si>
+    <t>Сайт</t>
+  </si>
+  <si>
     <t>Серійний номер пристрою</t>
   </si>
   <si>
@@ -63,15 +55,27 @@
     <t>Райони</t>
   </si>
   <si>
+    <t># Кількість модульних відсіків</t>
+  </si>
+  <si>
+    <t># Активні модульні відсіки</t>
+  </si>
+  <si>
     <t># Замінених модулів за період</t>
   </si>
   <si>
+    <t># Модулі, позначені як не використовувати</t>
+  </si>
+  <si>
     <t>&lt;#&gt;</t>
   </si>
   <si>
     <t>&lt;deviceName&gt;</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;deviceSerial&gt;</t>
   </si>
   <si>
@@ -81,22 +85,13 @@
     <t>&lt;Lga&gt;</t>
   </si>
   <si>
+    <t>&lt;moduleBayCapacity&gt;</t>
+  </si>
+  <si>
+    <t>&lt;activeModuleBays&gt;</t>
+  </si>
+  <si>
     <t>&lt;replacedModules&gt;</t>
-  </si>
-  <si>
-    <t># Активні модульні відсіки</t>
-  </si>
-  <si>
-    <t># Кількість модульних відсіків</t>
-  </si>
-  <si>
-    <t># Модулі, позначені як не використовувати</t>
-  </si>
-  <si>
-    <t>&lt;moduleBayCapacity&gt;</t>
-  </si>
-  <si>
-    <t>&lt;activeModuleBays&gt;</t>
   </si>
   <si>
     <t>&lt;disabledModules&gt;</t>
@@ -108,39 +103,39 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="204"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -166,46 +161,24 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -219,89 +192,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -609,56 +514,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.5703125"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="1"/>
     <col min="2" max="2" width="37.7109375" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
-    <col min="6" max="6" width="32.7109375" customWidth="1"/>
-    <col min="7" max="7" width="37.5703125" customWidth="1"/>
-    <col min="8" max="8" width="34.7109375" customWidth="1"/>
-    <col min="9" max="9" width="51" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="32.7109375" customWidth="1"/>
+    <col min="8" max="8" width="37.5703125" customWidth="1"/>
+    <col min="9" max="9" width="34.7109375" customWidth="1"/>
+    <col min="10" max="10" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -675,55 +581,62 @@
         <v>10</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="6" t="s">
+      <c r="H9" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:I9" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A8:I9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/module_status_report/uk.xlsx
+++ b/api/templates/module_status_report/uk.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7535F1-CD02-6A43-9944-2B53AA9EADED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="ModuleStatus" state="visible" r:id="rId4"/>
+    <sheet name="ModuleStatus" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">ModuleStatus!$A$8:$I$9</definedName>
@@ -40,9 +41,6 @@
     <t>#</t>
   </si>
   <si>
-    <t>Ім'я пристрою</t>
-  </si>
-  <si>
     <t>Сайт</t>
   </si>
   <si>
@@ -98,44 +96,47 @@
   </si>
   <si>
     <t>* Модулі позначені як "Не використовуються" на момент формування звіту &lt;ReportDate&gt;</t>
+  </si>
+  <si>
+    <t>Пристрій</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -161,24 +162,46 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -514,129 +537,128 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.5703125"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" customWidth="1"/>
-    <col min="2" max="2" width="37.7109375" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="32.7109375" customWidth="1"/>
-    <col min="8" max="8" width="37.5703125" customWidth="1"/>
-    <col min="9" max="9" width="34.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.5" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="36.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.5" customWidth="1"/>
+    <col min="6" max="6" width="16.5" customWidth="1"/>
+    <col min="7" max="7" width="32.6640625" customWidth="1"/>
+    <col min="8" max="8" width="37.5" customWidth="1"/>
+    <col min="9" max="9" width="34.6640625" customWidth="1"/>
     <col min="10" max="10" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="4" t="s">
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="I9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="J9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="7" t="s">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A8:I9"/>
+  <autoFilter ref="A8:I9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/module_status_report/uk.xlsx
+++ b/api/templates/module_status_report/uk.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7535F1-CD02-6A43-9944-2B53AA9EADED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="16000"/>
   </bookViews>
   <sheets>
-    <sheet name="ModuleStatus" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="ModuleStatus" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">ModuleStatus!$A$8:$I$9</definedName>
@@ -18,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Звіт про статус модуля</t>
   </si>
@@ -35,12 +34,18 @@
     <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
     <t>#</t>
   </si>
   <si>
+    <t>Пристрій</t>
+  </si>
+  <si>
     <t>Сайт</t>
   </si>
   <si>
@@ -96,47 +101,44 @@
   </si>
   <si>
     <t>* Модулі позначені як "Не використовуються" на момент формування звіту &lt;ReportDate&gt;</t>
-  </si>
-  <si>
-    <t>Пристрій</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="204"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -162,46 +164,24 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -537,9 +517,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.5"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -553,112 +533,117 @@
     <col min="10" max="10" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:I9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A8:I9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/module_status_report/uk.xlsx
+++ b/api/templates/module_status_report/uk.xlsx
@@ -188,10 +188,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -563,7 +564,7 @@
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -573,66 +574,66 @@
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="8" t="s">
         <v>26</v>
       </c>
     </row>

--- a/api/templates/module_status_report/uk.xlsx
+++ b/api/templates/module_status_report/uk.xlsx
@@ -34,7 +34,7 @@
     <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Виведені з експлуатації пристрої: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -188,11 +188,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -564,7 +563,7 @@
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -574,66 +573,66 @@
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="7" t="s">
         <v>26</v>
       </c>
     </row>
